--- a/Results/TestCases/XLSX/changePassword_TestCases.xlsx
+++ b/Results/TestCases/XLSX/changePassword_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_PASSWORD_02</t>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>Verify validation error on entering short new password</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_PASSWORD_11</t>
@@ -229,7 +232,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -249,12 +252,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,7 +277,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -310,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -319,6 +333,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1054,13 +1071,13 @@
       <c r="J11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+      <c r="K11" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,13 +1086,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1095,7 +1112,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1121,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1130,7 +1147,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1156,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1165,7 +1182,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1191,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1200,7 +1217,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1226,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1235,7 +1252,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,13 +1261,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1270,7 +1287,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,13 +1296,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1305,7 +1322,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,13 +1331,13 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -1340,7 +1357,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1366,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1375,7 +1392,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1401,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1410,7 +1427,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1436,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1445,7 +1462,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,13 +1471,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1480,7 +1497,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1506,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1515,7 +1532,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1550,7 +1567,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1576,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>

--- a/Results/TestCases/XLSX/changePassword_TestCases.xlsx
+++ b/Results/TestCases/XLSX/changePassword_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="105">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,15 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the Change Password page.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The browser URL should match a value matching /updatePassword/
+- The orangehrm main title element should display the text 'Update Password'
+- The password element should be visible</t>
   </si>
   <si>
     <t>High</t>
@@ -81,6 +81,13 @@
     <t>Verify validation messages on empty form submission</t>
   </si>
   <si>
+    <t>1. Click the submit element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The count should be greater than or equal to '1'
+- The required messages.nth(i) should display the text a value matching /Required|Should have at least|Passwords do not match/</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_03</t>
   </si>
   <si>
@@ -90,12 +97,27 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Enter 'admin123' into the password element
+2. Enter 'NewPass123!' into the password element
+3. Enter 'DifferentPass123!' into the password element
+4. Click the submit element</t>
+  </si>
+  <si>
+    <t>- The mismatch error should display the text a value matching /Passwords do not match/</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_04</t>
   </si>
   <si>
     <t>Verify cancel button redirects back to dashboard</t>
   </si>
   <si>
+    <t>1. Click the oxd button  ghost element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/dashboard/index'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -105,18 +127,27 @@
     <t>Verify page URL contains updatePassword</t>
   </si>
   <si>
+    <t>- The page.url() should contain 'updatePassword'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_06</t>
   </si>
   <si>
     <t>Verify heading title has class orangehrm-main-title</t>
   </si>
   <si>
+    <t>- The orangehrm main title element should have a CSS class matching a value matching /orangehrm-main-title/</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_07</t>
   </si>
   <si>
     <t>Verify current password field type attribute is password</t>
   </si>
   <si>
+    <t>- The type should equal 'password'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_08</t>
   </si>
   <si>
@@ -135,7 +166,12 @@
     <t>Verify validation error on entering short new password</t>
   </si>
   <si>
-    <t>FAILED</t>
+    <t xml:space="preserve">1. Enter '123' into the password element
+2. Press the 'Tab' key while focused on the password element
+3. Click the submit element</t>
+  </si>
+  <si>
+    <t>- The err should display the text a value matching /Should have at least/</t>
   </si>
   <si>
     <t>TC_PASSWORD_11</t>
@@ -144,12 +180,18 @@
     <t>Verify current password input autocomplete settings</t>
   </si>
   <si>
+    <t>- The autocomplete === null || autocomplete === 'off' should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_12</t>
   </si>
   <si>
     <t>Verify cancel button tag name is button</t>
   </si>
   <si>
+    <t>- The tag name should equal 'button'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_13</t>
   </si>
   <si>
@@ -162,18 +204,27 @@
     <t>Verify cancel button has default ghost class</t>
   </si>
   <si>
+    <t>- The oxd button  ghost element should have a CSS class matching a value matching /oxd-button--ghost/</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_15</t>
   </si>
   <si>
     <t>Verify save button has secondary submit class</t>
   </si>
   <si>
+    <t>- The submit element should have a CSS class matching a value matching /oxd-button--secondary/</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_16</t>
   </si>
   <si>
     <t>Verify cursor hover properties on cancel button</t>
   </si>
   <si>
+    <t>- The cursor should equal 'pointer'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_17</t>
   </si>
   <si>
@@ -186,6 +237,13 @@
     <t>Verify tab index flow from current password input</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Focus the password element
+2. Press the 'Tab' key</t>
+  </si>
+  <si>
+    <t>- The password element should receive keyboard focus</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_19</t>
   </si>
   <si>
@@ -198,41 +256,96 @@
     <t>Verify tab index flow from confirm password input</t>
   </si>
   <si>
+    <t>- The oxd button  ghost element should receive keyboard focus</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_21</t>
   </si>
   <si>
     <t>Verify HTML lang tag exists in document root</t>
   </si>
   <si>
+    <t>- The lang === null || lang === 'en' should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_22</t>
   </si>
   <si>
     <t>Verify secure connection protocol is HTTPS</t>
   </si>
   <si>
+    <t>- The page.url().starts with('https://') should equal 'true'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_23</t>
   </si>
   <si>
     <t>Verify page title contains OrangeHRM</t>
   </si>
   <si>
+    <t>- The title should contain 'OrangeHRM'</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_24</t>
   </si>
   <si>
     <t>Verify form element wrapping exists</t>
   </si>
   <si>
+    <t>- The oxd form element should be visible</t>
+  </si>
+  <si>
     <t>TC_PASSWORD_25</t>
   </si>
   <si>
     <t>Verify Username input or label exists in userarea</t>
+  </si>
+  <si>
+    <t>- The userarea should be visible</t>
+  </si>
+  <si>
+    <t>TC_PASSWORD_26</t>
+  </si>
+  <si>
+    <t>Verify Required validation is shown when Current Password is left empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'NewPass123!' into the password element
+2. Click the submit element</t>
+  </si>
+  <si>
+    <t>- The err should display the text 'Required'</t>
+  </si>
+  <si>
+    <t>TC_PASSWORD_27</t>
+  </si>
+  <si>
+    <t>Verify a new password just below the minimum length boundary is rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter 'Ab1@56' into the password element
+2. Press the 'Tab' key while focused on the password element
+3. Click the submit element</t>
+  </si>
+  <si>
+    <t>TC_PASSWORD_28</t>
+  </si>
+  <si>
+    <t>Verify New Password field correctly accepts and displays typed characters</t>
+  </si>
+  <si>
+    <t>1. Enter 'TempCheck123!' into the password element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The value should equal 'TempCheck123!'
+- The length should equal '13'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -256,14 +369,8 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FFA51D24"/>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -278,11 +385,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -333,9 +435,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -677,7 +776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -783,10 +882,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -797,7 +896,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -806,22 +905,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -832,7 +931,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -841,25 +940,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -867,7 +966,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -876,13 +975,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -891,10 +990,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -902,7 +1001,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -911,13 +1010,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -926,10 +1025,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -937,7 +1036,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -946,13 +1045,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -961,10 +1060,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -972,7 +1071,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -981,13 +1080,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -996,10 +1095,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -1007,7 +1106,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1016,13 +1115,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1031,10 +1130,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1042,7 +1141,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1051,33 +1150,33 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1086,13 +1185,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1101,10 +1200,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1112,7 +1211,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1121,13 +1220,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1136,10 +1235,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1147,7 +1246,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1156,13 +1255,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1171,10 +1270,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1182,7 +1281,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1191,13 +1290,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1206,10 +1305,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1217,7 +1316,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1226,13 +1325,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1241,10 +1340,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1252,7 +1351,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1261,13 +1360,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1276,10 +1375,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1287,7 +1386,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1296,13 +1395,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -1311,10 +1410,10 @@
         <v>16</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1322,7 +1421,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1331,25 +1430,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1357,7 +1456,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1366,25 +1465,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1392,7 +1491,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1401,25 +1500,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1427,7 +1526,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1436,13 +1535,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1451,10 +1550,10 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1462,7 +1561,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1471,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1486,10 +1585,10 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1497,7 +1596,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1506,13 +1605,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1521,10 +1620,10 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1532,7 +1631,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1541,13 +1640,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1556,10 +1655,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1567,7 +1666,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1576,13 +1675,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1591,12 +1690,117 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Results/TestCases/XLSX/changePassword_TestCases.xlsx
+++ b/Results/TestCases/XLSX/changePassword_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="106">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>- The userarea should be visible</t>
+  </si>
+  <si>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_PASSWORD_26</t>
@@ -345,7 +348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -369,8 +372,14 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -385,6 +394,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1E7DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -426,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -435,6 +449,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1695,13 +1712,13 @@
       <c r="J26" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+      <c r="K26" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1710,22 +1727,22 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>33</v>
@@ -1736,7 +1753,7 @@
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1745,19 +1762,19 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>50</v>
@@ -1765,13 +1782,13 @@
       <c r="J28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>19</v>
+      <c r="K28" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
@@ -1780,22 +1797,22 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>33</v>
